--- a/src/fixtures/sample/gstr2b-2025-11.xlsx
+++ b/src/fixtures/sample/gstr2b-2025-11.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:O44"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -517,25 +517,25 @@
         <v>Mahesh Steel Traders</v>
       </c>
       <c r="C7" t="str">
-        <v>S01/2025/011</v>
+        <v>S01/2025/021</v>
       </c>
       <c r="D7" t="str">
-        <v>17/10/2025</v>
+        <v>16/11/2025</v>
       </c>
       <c r="E7">
-        <v>579380</v>
+        <v>552240</v>
       </c>
       <c r="F7">
-        <v>491000</v>
+        <v>468000</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>44190</v>
+        <v>42120</v>
       </c>
       <c r="I7">
-        <v>44190</v>
+        <v>42120</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -544,7 +544,7 @@
         <v>2025-12</v>
       </c>
       <c r="L7" t="str">
-        <v>14/12/2025</v>
+        <v>12/12/2025</v>
       </c>
       <c r="M7" t="str">
         <v>Yes</v>
@@ -558,31 +558,31 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>27AAPFM4821K1ZV</v>
+        <v>24AAGCA1188M1ZI</v>
       </c>
       <c r="B8" t="str">
-        <v>Mahesh Steel Traders</v>
+        <v>Anand Polymers</v>
       </c>
       <c r="C8" t="str">
-        <v>S01/2025/021</v>
+        <v>S05/2025/021</v>
       </c>
       <c r="D8" t="str">
-        <v>15/11/2025</v>
+        <v>19/11/2025</v>
       </c>
       <c r="E8">
-        <v>580560</v>
+        <v>359900</v>
       </c>
       <c r="F8">
-        <v>492000</v>
+        <v>305000</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>54900</v>
       </c>
       <c r="H8">
-        <v>44280</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>44280</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -591,7 +591,7 @@
         <v>2025-12</v>
       </c>
       <c r="L8" t="str">
-        <v>13/12/2025</v>
+        <v>16/12/2025</v>
       </c>
       <c r="M8" t="str">
         <v>Yes</v>
@@ -605,31 +605,31 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>27AAPFM4821K1ZV</v>
+        <v>24AAGCA1188M1ZI</v>
       </c>
       <c r="B9" t="str">
-        <v>Mahesh Steel Traders</v>
+        <v>Anand Polymers</v>
       </c>
       <c r="C9" t="str">
-        <v>S01/2025/022</v>
+        <v>S05/2025/022</v>
       </c>
       <c r="D9" t="str">
-        <v>20/11/2025</v>
+        <v>23/11/2025</v>
       </c>
       <c r="E9">
-        <v>568760</v>
+        <v>372880</v>
       </c>
       <c r="F9">
-        <v>482000</v>
+        <v>316000</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>56880</v>
       </c>
       <c r="H9">
-        <v>43380</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>43380</v>
+        <v>0</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -638,7 +638,7 @@
         <v>2025-12</v>
       </c>
       <c r="L9" t="str">
-        <v>08/12/2025</v>
+        <v>14/12/2025</v>
       </c>
       <c r="M9" t="str">
         <v>Yes</v>
@@ -658,19 +658,19 @@
         <v>Anand Polymers</v>
       </c>
       <c r="C10" t="str">
-        <v>S05/2025/021</v>
+        <v>S05/2025/023</v>
       </c>
       <c r="D10" t="str">
-        <v>13/11/2025</v>
+        <v>12/11/2025</v>
       </c>
       <c r="E10">
-        <v>376420</v>
+        <v>363440</v>
       </c>
       <c r="F10">
-        <v>319000</v>
+        <v>308000</v>
       </c>
       <c r="G10">
-        <v>57420</v>
+        <v>55440</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -685,7 +685,7 @@
         <v>2025-12</v>
       </c>
       <c r="L10" t="str">
-        <v>08/12/2025</v>
+        <v>14/12/2025</v>
       </c>
       <c r="M10" t="str">
         <v>Yes</v>
@@ -699,31 +699,31 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24AAGCA1188M1ZI</v>
+        <v>27AABFS9034J1ZY</v>
       </c>
       <c r="B11" t="str">
-        <v>Anand Polymers</v>
+        <v>Surya Electricals</v>
       </c>
       <c r="C11" t="str">
-        <v>S05/2025/022</v>
+        <v>SE 21</v>
       </c>
       <c r="D11" t="str">
-        <v>20/11/2025</v>
+        <v>09/11/2025</v>
       </c>
       <c r="E11">
-        <v>355180</v>
+        <v>178180</v>
       </c>
       <c r="F11">
-        <v>301000</v>
+        <v>151000</v>
       </c>
       <c r="G11">
-        <v>54180</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>13590</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>13590</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -732,7 +732,7 @@
         <v>2025-12</v>
       </c>
       <c r="L11" t="str">
-        <v>08/12/2025</v>
+        <v>13/12/2025</v>
       </c>
       <c r="M11" t="str">
         <v>Yes</v>
@@ -746,31 +746,31 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>24AAGCA1188M1ZI</v>
+        <v>27AABFS9034J1ZY</v>
       </c>
       <c r="B12" t="str">
-        <v>Anand Polymers</v>
+        <v>Surya Electricals</v>
       </c>
       <c r="C12" t="str">
-        <v>S05/2025/023</v>
+        <v>SE 21</v>
       </c>
       <c r="D12" t="str">
-        <v>02/11/2025</v>
+        <v>17/11/2025</v>
       </c>
       <c r="E12">
-        <v>368160</v>
+        <v>155760</v>
       </c>
       <c r="F12">
-        <v>312000</v>
+        <v>132000</v>
       </c>
       <c r="G12">
-        <v>56160</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>11880</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>11880</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -779,7 +779,7 @@
         <v>2025-12</v>
       </c>
       <c r="L12" t="str">
-        <v>10/12/2025</v>
+        <v>11/12/2025</v>
       </c>
       <c r="M12" t="str">
         <v>Yes</v>
@@ -793,31 +793,31 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>27AABFS9034J1ZY</v>
+        <v>27AAJFN2276C1ZC</v>
       </c>
       <c r="B13" t="str">
-        <v>Surya Electricals</v>
+        <v>Nilkanth Traders</v>
       </c>
       <c r="C13" t="str">
-        <v>SE 21</v>
+        <v>S07/2025/021</v>
       </c>
       <c r="D13" t="str">
-        <v>19/11/2025</v>
+        <v>12/11/2025</v>
       </c>
       <c r="E13">
-        <v>166380</v>
+        <v>253700</v>
       </c>
       <c r="F13">
-        <v>141000</v>
+        <v>215000</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>12690</v>
+        <v>19350</v>
       </c>
       <c r="I13">
-        <v>12690</v>
+        <v>19350</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -826,7 +826,7 @@
         <v>2025-12</v>
       </c>
       <c r="L13" t="str">
-        <v>08/12/2025</v>
+        <v>09/12/2025</v>
       </c>
       <c r="M13" t="str">
         <v>Yes</v>
@@ -840,31 +840,31 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>27AABFS9034J1ZY</v>
+        <v>27AAJFN2276C1ZC</v>
       </c>
       <c r="B14" t="str">
-        <v>Surya Electricals</v>
+        <v>Nilkanth Traders</v>
       </c>
       <c r="C14" t="str">
-        <v>SE 21</v>
+        <v>S07/2025/022</v>
       </c>
       <c r="D14" t="str">
-        <v>04/11/2025</v>
+        <v>21/11/2025</v>
       </c>
       <c r="E14">
-        <v>166380</v>
+        <v>239540</v>
       </c>
       <c r="F14">
-        <v>141000</v>
+        <v>203000</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>12690</v>
+        <v>18270</v>
       </c>
       <c r="I14">
-        <v>12690</v>
+        <v>18270</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -873,7 +873,7 @@
         <v>2025-12</v>
       </c>
       <c r="L14" t="str">
-        <v>09/12/2025</v>
+        <v>11/12/2025</v>
       </c>
       <c r="M14" t="str">
         <v>Yes</v>
@@ -887,31 +887,31 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>27AAJFN2276C1ZC</v>
+        <v>24AAECR8890P1ZI</v>
       </c>
       <c r="B15" t="str">
-        <v>Nilkanth Traders</v>
+        <v>Ratna Chemicals</v>
       </c>
       <c r="C15" t="str">
-        <v>S07/2025/021</v>
+        <v>S08/2025/021</v>
       </c>
       <c r="D15" t="str">
-        <v>26/11/2025</v>
+        <v>04/11/2025</v>
       </c>
       <c r="E15">
-        <v>236000</v>
+        <v>195880</v>
       </c>
       <c r="F15">
-        <v>200000</v>
+        <v>166000</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>29880</v>
       </c>
       <c r="H15">
-        <v>18000</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>18000</v>
+        <v>0</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>2025-12</v>
       </c>
       <c r="L15" t="str">
-        <v>15/12/2025</v>
+        <v>10/12/2025</v>
       </c>
       <c r="M15" t="str">
         <v>Yes</v>
@@ -934,31 +934,31 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>27AAJFN2276C1ZC</v>
+        <v>24AAECR8890P1ZI</v>
       </c>
       <c r="B16" t="str">
-        <v>Nilkanth Traders</v>
+        <v>Ratna Chemicals</v>
       </c>
       <c r="C16" t="str">
-        <v>S07/2025/022</v>
+        <v>S08/2025/022</v>
       </c>
       <c r="D16" t="str">
-        <v>16/11/2025</v>
+        <v>17/11/2025</v>
       </c>
       <c r="E16">
-        <v>245440</v>
+        <v>207680</v>
       </c>
       <c r="F16">
-        <v>208000</v>
+        <v>176000</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>31680</v>
       </c>
       <c r="H16">
-        <v>18720</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>18720</v>
+        <v>0</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -967,7 +967,7 @@
         <v>2025-12</v>
       </c>
       <c r="L16" t="str">
-        <v>08/12/2025</v>
+        <v>10/12/2025</v>
       </c>
       <c r="M16" t="str">
         <v>Yes</v>
@@ -981,31 +981,31 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>24AAECR8890P1ZI</v>
+        <v>27AAACM6543N1Z3</v>
       </c>
       <c r="B17" t="str">
-        <v>Ratna Chemicals</v>
+        <v>Metro Motors</v>
       </c>
       <c r="C17" t="str">
-        <v>S08/2025/021</v>
+        <v>S09/2025/021</v>
       </c>
       <c r="D17" t="str">
-        <v>21/11/2025</v>
+        <v>16/11/2025</v>
       </c>
       <c r="E17">
-        <v>207680</v>
+        <v>1047840</v>
       </c>
       <c r="F17">
-        <v>176000</v>
+        <v>888000</v>
       </c>
       <c r="G17">
-        <v>31680</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>79920</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>79920</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -1014,13 +1014,13 @@
         <v>2025-12</v>
       </c>
       <c r="L17" t="str">
-        <v>11/12/2025</v>
+        <v>15/12/2025</v>
       </c>
       <c r="M17" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="N17" t="str">
-        <v/>
+        <v>ITC unavailable - blocked credit</v>
       </c>
       <c r="O17" t="str">
         <v>N</v>
@@ -1028,25 +1028,25 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>24AAECR8890P1ZI</v>
+        <v>27AAFCV4412Q2ZU</v>
       </c>
       <c r="B18" t="str">
-        <v>Ratna Chemicals</v>
+        <v>Vindhya Alloys</v>
       </c>
       <c r="C18" t="str">
-        <v>S08/2025/022</v>
+        <v>S10/2025/021</v>
       </c>
       <c r="D18" t="str">
-        <v>19/11/2025</v>
+        <v>21/11/2025</v>
       </c>
       <c r="E18">
-        <v>207680</v>
+        <v>295000</v>
       </c>
       <c r="F18">
-        <v>176000</v>
+        <v>250000</v>
       </c>
       <c r="G18">
-        <v>31680</v>
+        <v>45000</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -1061,7 +1061,7 @@
         <v>2025-12</v>
       </c>
       <c r="L18" t="str">
-        <v>11/12/2025</v>
+        <v>16/12/2025</v>
       </c>
       <c r="M18" t="str">
         <v>Yes</v>
@@ -1075,31 +1075,31 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>27AAACM6543N1Z3</v>
+        <v>27AAFCV4412Q2ZU</v>
       </c>
       <c r="B19" t="str">
-        <v>Metro Motors</v>
+        <v>Vindhya Alloys</v>
       </c>
       <c r="C19" t="str">
-        <v>S09/2025/021</v>
+        <v>S10/2025/022</v>
       </c>
       <c r="D19" t="str">
-        <v>17/11/2025</v>
+        <v>10/11/2025</v>
       </c>
       <c r="E19">
-        <v>1053740</v>
+        <v>311520</v>
       </c>
       <c r="F19">
-        <v>893000</v>
+        <v>264000</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>47520</v>
       </c>
       <c r="H19">
-        <v>80370</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>80370</v>
+        <v>0</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -1108,13 +1108,13 @@
         <v>2025-12</v>
       </c>
       <c r="L19" t="str">
-        <v>15/12/2025</v>
+        <v>13/12/2025</v>
       </c>
       <c r="M19" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="N19" t="str">
-        <v>ITC unavailable - blocked credit</v>
+        <v/>
       </c>
       <c r="O19" t="str">
         <v>N</v>
@@ -1122,31 +1122,31 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>27AAFCV4412Q2ZU</v>
+        <v>27AAFCB2210G1Z8</v>
       </c>
       <c r="B20" t="str">
-        <v>Vindhya Alloys</v>
+        <v>Bharat Office Supplies</v>
       </c>
       <c r="C20" t="str">
-        <v>S10/2025/021</v>
+        <v>S12/2025/022</v>
       </c>
       <c r="D20" t="str">
-        <v>26/11/2025</v>
+        <v>18/11/2025</v>
       </c>
       <c r="E20">
-        <v>322140</v>
+        <v>193520</v>
       </c>
       <c r="F20">
-        <v>273000</v>
+        <v>164000</v>
       </c>
       <c r="G20">
-        <v>49140</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>14760</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>14760</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -1155,7 +1155,7 @@
         <v>2025-12</v>
       </c>
       <c r="L20" t="str">
-        <v>13/12/2025</v>
+        <v>12/12/2025</v>
       </c>
       <c r="M20" t="str">
         <v>Yes</v>
@@ -1169,31 +1169,31 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>27AAFCV4412Q2ZU</v>
+        <v>27AAGFK5561R1ZL</v>
       </c>
       <c r="B21" t="str">
-        <v>Vindhya Alloys</v>
+        <v>Konkan Hardware</v>
       </c>
       <c r="C21" t="str">
-        <v>S10/2025/022</v>
+        <v>S13/2025/021</v>
       </c>
       <c r="D21" t="str">
-        <v>08/11/2025</v>
+        <v>21/11/2025</v>
       </c>
       <c r="E21">
-        <v>300900</v>
+        <v>100300</v>
       </c>
       <c r="F21">
-        <v>255000</v>
+        <v>85000</v>
       </c>
       <c r="G21">
-        <v>45900</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>7650</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>7650</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -1202,7 +1202,7 @@
         <v>2025-12</v>
       </c>
       <c r="L21" t="str">
-        <v>08/12/2025</v>
+        <v>14/12/2025</v>
       </c>
       <c r="M21" t="str">
         <v>Yes</v>
@@ -1216,31 +1216,31 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>27AAFCB2210G1Z8</v>
+        <v>24AAACT3398E1ZE</v>
       </c>
       <c r="B22" t="str">
-        <v>Bharat Office Supplies</v>
+        <v>Trident Paper Mills</v>
       </c>
       <c r="C22" t="str">
-        <v>S12/2025/021</v>
+        <v>S14/2025/021</v>
       </c>
       <c r="D22" t="str">
-        <v>10/11/2025</v>
+        <v>26/11/2025</v>
       </c>
       <c r="E22">
-        <v>180540</v>
+        <v>162840</v>
       </c>
       <c r="F22">
-        <v>153000</v>
+        <v>138000</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>24840</v>
       </c>
       <c r="H22">
-        <v>13770</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>13770</v>
+        <v>0</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -1249,7 +1249,7 @@
         <v>2025-12</v>
       </c>
       <c r="L22" t="str">
-        <v>15/12/2025</v>
+        <v>10/12/2025</v>
       </c>
       <c r="M22" t="str">
         <v>Yes</v>
@@ -1263,31 +1263,31 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>27AAFCB2210G1Z8</v>
+        <v>33AAJFL7745T1ZE</v>
       </c>
       <c r="B23" t="str">
-        <v>Bharat Office Supplies</v>
+        <v>Lakshmi Fasteners</v>
       </c>
       <c r="C23" t="str">
-        <v>S12/2025/022</v>
+        <v>S15/2025/021</v>
       </c>
       <c r="D23" t="str">
-        <v>07/11/2025</v>
+        <v>22/11/2025</v>
       </c>
       <c r="E23">
-        <v>205320</v>
+        <v>51920</v>
       </c>
       <c r="F23">
-        <v>174000</v>
+        <v>44000</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>7920</v>
       </c>
       <c r="H23">
-        <v>15660</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>15660</v>
+        <v>0</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -1296,7 +1296,7 @@
         <v>2025-12</v>
       </c>
       <c r="L23" t="str">
-        <v>13/12/2025</v>
+        <v>16/12/2025</v>
       </c>
       <c r="M23" t="str">
         <v>Yes</v>
@@ -1310,31 +1310,31 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>27AAGFK5561R1ZL</v>
+        <v>33AAJFL7745T1ZE</v>
       </c>
       <c r="B24" t="str">
-        <v>Konkan Hardware</v>
+        <v>Lakshmi Fasteners</v>
       </c>
       <c r="C24" t="str">
-        <v>S13/2025/021</v>
+        <v>S15/2025/022</v>
       </c>
       <c r="D24" t="str">
-        <v>24/11/2025</v>
+        <v>13/11/2025</v>
       </c>
       <c r="E24">
-        <v>75520</v>
+        <v>54280</v>
       </c>
       <c r="F24">
-        <v>64000</v>
+        <v>46000</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>8280</v>
       </c>
       <c r="H24">
-        <v>5760</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>5760</v>
+        <v>0</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -1343,7 +1343,7 @@
         <v>2025-12</v>
       </c>
       <c r="L24" t="str">
-        <v>08/12/2025</v>
+        <v>12/12/2025</v>
       </c>
       <c r="M24" t="str">
         <v>Yes</v>
@@ -1357,25 +1357,25 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>24AAACT3398E1ZE</v>
+        <v>33AAJFL7745T1ZE</v>
       </c>
       <c r="B25" t="str">
-        <v>Trident Paper Mills</v>
+        <v>Lakshmi Fasteners</v>
       </c>
       <c r="C25" t="str">
-        <v>S14/2025/021</v>
+        <v>S15/2025/023</v>
       </c>
       <c r="D25" t="str">
-        <v>14/11/2025</v>
+        <v>22/11/2025</v>
       </c>
       <c r="E25">
-        <v>147500</v>
+        <v>57820</v>
       </c>
       <c r="F25">
-        <v>125000</v>
+        <v>49000</v>
       </c>
       <c r="G25">
-        <v>22500</v>
+        <v>8820</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>2025-12</v>
       </c>
       <c r="L25" t="str">
-        <v>13/12/2025</v>
+        <v>08/12/2025</v>
       </c>
       <c r="M25" t="str">
         <v>Yes</v>
@@ -1404,25 +1404,25 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>33AAJFL7745T1ZE</v>
+        <v>29AAECO9912W1Z8</v>
       </c>
       <c r="B26" t="str">
-        <v>Lakshmi Fasteners</v>
+        <v>Orion Software Services</v>
       </c>
       <c r="C26" t="str">
-        <v>S15/2025/021</v>
+        <v>S16/2025/021</v>
       </c>
       <c r="D26" t="str">
-        <v>19/11/2025</v>
+        <v>14/11/2025</v>
       </c>
       <c r="E26">
-        <v>36580</v>
+        <v>62540</v>
       </c>
       <c r="F26">
-        <v>31000</v>
+        <v>53000</v>
       </c>
       <c r="G26">
-        <v>5580</v>
+        <v>9540</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -1451,25 +1451,25 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>33AAJFL7745T1ZE</v>
+        <v>29AAECO9912W1Z8</v>
       </c>
       <c r="B27" t="str">
-        <v>Lakshmi Fasteners</v>
+        <v>Orion Software Services</v>
       </c>
       <c r="C27" t="str">
-        <v>S15/2025/022</v>
+        <v>S16/2025/022</v>
       </c>
       <c r="D27" t="str">
-        <v>04/11/2025</v>
+        <v>11/11/2025</v>
       </c>
       <c r="E27">
-        <v>42480</v>
+        <v>70800</v>
       </c>
       <c r="F27">
-        <v>36000</v>
+        <v>60000</v>
       </c>
       <c r="G27">
-        <v>6480</v>
+        <v>10800</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -1484,7 +1484,7 @@
         <v>2025-12</v>
       </c>
       <c r="L27" t="str">
-        <v>12/12/2025</v>
+        <v>16/12/2025</v>
       </c>
       <c r="M27" t="str">
         <v>Yes</v>
@@ -1498,25 +1498,25 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>33AAJFL7745T1ZE</v>
+        <v>09AAHFG4423Y1ZH</v>
       </c>
       <c r="B28" t="str">
-        <v>Lakshmi Fasteners</v>
+        <v>Ganga Textiles</v>
       </c>
       <c r="C28" t="str">
-        <v>S15/2025/023</v>
+        <v>S17/2025/021</v>
       </c>
       <c r="D28" t="str">
-        <v>07/11/2025</v>
+        <v>22/11/2025</v>
       </c>
       <c r="E28">
-        <v>31860</v>
+        <v>57820</v>
       </c>
       <c r="F28">
-        <v>27000</v>
+        <v>49000</v>
       </c>
       <c r="G28">
-        <v>4860</v>
+        <v>8820</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -1531,7 +1531,7 @@
         <v>2025-12</v>
       </c>
       <c r="L28" t="str">
-        <v>08/12/2025</v>
+        <v>10/12/2025</v>
       </c>
       <c r="M28" t="str">
         <v>Yes</v>
@@ -1545,31 +1545,31 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>29AAECO9912W1Z8</v>
+        <v>27AAKFP6678U1ZU</v>
       </c>
       <c r="B29" t="str">
-        <v>Orion Software Services</v>
+        <v>Pinnacle Safety Gear</v>
       </c>
       <c r="C29" t="str">
-        <v>S16/2025/021</v>
+        <v>S18/2025/021</v>
       </c>
       <c r="D29" t="str">
-        <v>24/11/2025</v>
+        <v>09/11/2025</v>
       </c>
       <c r="E29">
-        <v>71980</v>
+        <v>160480</v>
       </c>
       <c r="F29">
-        <v>61000</v>
+        <v>136000</v>
       </c>
       <c r="G29">
-        <v>10980</v>
+        <v>0</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>12240</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>12240</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -1578,7 +1578,7 @@
         <v>2025-12</v>
       </c>
       <c r="L29" t="str">
-        <v>08/12/2025</v>
+        <v>15/12/2025</v>
       </c>
       <c r="M29" t="str">
         <v>Yes</v>
@@ -1592,31 +1592,31 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>29AAECO9912W1Z8</v>
+        <v>27AAKFP6678U1ZU</v>
       </c>
       <c r="B30" t="str">
-        <v>Orion Software Services</v>
+        <v>Pinnacle Safety Gear</v>
       </c>
       <c r="C30" t="str">
-        <v>S16/2025/022</v>
+        <v>S18/2025/022</v>
       </c>
       <c r="D30" t="str">
-        <v>26/11/2025</v>
+        <v>25/11/2025</v>
       </c>
       <c r="E30">
-        <v>71980</v>
+        <v>165200</v>
       </c>
       <c r="F30">
-        <v>61000</v>
+        <v>140000</v>
       </c>
       <c r="G30">
-        <v>10980</v>
+        <v>0</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>12600</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>12600</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -1625,7 +1625,7 @@
         <v>2025-12</v>
       </c>
       <c r="L30" t="str">
-        <v>16/12/2025</v>
+        <v>09/12/2025</v>
       </c>
       <c r="M30" t="str">
         <v>Yes</v>
@@ -1639,31 +1639,31 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>09AAHFG4423Y1ZH</v>
+        <v>27AAKFP6678U1ZU</v>
       </c>
       <c r="B31" t="str">
-        <v>Ganga Textiles</v>
+        <v>Pinnacle Safety Gear</v>
       </c>
       <c r="C31" t="str">
-        <v>S17/2025/021</v>
+        <v>S18/2025/023</v>
       </c>
       <c r="D31" t="str">
-        <v>06/11/2025</v>
+        <v>02/11/2025</v>
       </c>
       <c r="E31">
-        <v>48380</v>
+        <v>161660</v>
       </c>
       <c r="F31">
-        <v>41000</v>
+        <v>137000</v>
       </c>
       <c r="G31">
-        <v>7380</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>12330</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>12330</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -1686,31 +1686,31 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>27AAKFP6678U1ZU</v>
+        <v>33AABFS2234V1ZT</v>
       </c>
       <c r="B32" t="str">
-        <v>Pinnacle Safety Gear</v>
+        <v>Sundar Printing Works</v>
       </c>
       <c r="C32" t="str">
-        <v>S18/2025/021</v>
+        <v>S19/2025/012</v>
       </c>
       <c r="D32" t="str">
-        <v>14/11/2025</v>
+        <v>09/10/2025</v>
       </c>
       <c r="E32">
-        <v>151040</v>
+        <v>116820</v>
       </c>
       <c r="F32">
-        <v>128000</v>
+        <v>99000</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>17820</v>
       </c>
       <c r="H32">
-        <v>11520</v>
+        <v>0</v>
       </c>
       <c r="I32">
-        <v>11520</v>
+        <v>0</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -1733,31 +1733,31 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>27AAKFP6678U1ZU</v>
+        <v>33AABFS2234V1ZT</v>
       </c>
       <c r="B33" t="str">
-        <v>Pinnacle Safety Gear</v>
+        <v>Sundar Printing Works</v>
       </c>
       <c r="C33" t="str">
-        <v>S18/2025/023</v>
+        <v>S19/2025/021</v>
       </c>
       <c r="D33" t="str">
-        <v>25/11/2025</v>
+        <v>08/11/2025</v>
       </c>
       <c r="E33">
-        <v>147500</v>
+        <v>110920</v>
       </c>
       <c r="F33">
-        <v>125000</v>
+        <v>94000</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>16920</v>
       </c>
       <c r="H33">
-        <v>11250</v>
+        <v>0</v>
       </c>
       <c r="I33">
-        <v>11250</v>
+        <v>0</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -1780,31 +1780,31 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>33AABFS2234V1ZT</v>
+        <v>27AAFCA8801X1ZT</v>
       </c>
       <c r="B34" t="str">
-        <v>Sundar Printing Works</v>
+        <v>Ashoka Civil Works</v>
       </c>
       <c r="C34" t="str">
-        <v>S19/2025/021</v>
+        <v>S20/2025/021</v>
       </c>
       <c r="D34" t="str">
-        <v>13/11/2025</v>
+        <v>20/11/2025</v>
       </c>
       <c r="E34">
-        <v>114460</v>
+        <v>158120</v>
       </c>
       <c r="F34">
-        <v>97000</v>
+        <v>134000</v>
       </c>
       <c r="G34">
-        <v>17460</v>
+        <v>0</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>12060</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>12060</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -1813,7 +1813,7 @@
         <v>2025-12</v>
       </c>
       <c r="L34" t="str">
-        <v>08/12/2025</v>
+        <v>12/12/2025</v>
       </c>
       <c r="M34" t="str">
         <v>Yes</v>
@@ -1827,31 +1827,31 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>33AABFS2234V1ZT</v>
+        <v>27AAFCA8801X1ZT</v>
       </c>
       <c r="B35" t="str">
-        <v>Sundar Printing Works</v>
+        <v>Ashoka Civil Works</v>
       </c>
       <c r="C35" t="str">
-        <v>S19/2025/022</v>
+        <v>S20/2025/022</v>
       </c>
       <c r="D35" t="str">
         <v>25/11/2025</v>
       </c>
       <c r="E35">
-        <v>112100</v>
+        <v>159300</v>
       </c>
       <c r="F35">
-        <v>95000</v>
+        <v>135000</v>
       </c>
       <c r="G35">
-        <v>17100</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>12150</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>12150</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>2025-12</v>
       </c>
       <c r="L35" t="str">
-        <v>10/12/2025</v>
+        <v>12/12/2025</v>
       </c>
       <c r="M35" t="str">
         <v>Yes</v>
@@ -1874,31 +1874,31 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>27AAFCA8801X1ZT</v>
+        <v>29AADCN3345Z1ZD</v>
       </c>
       <c r="B36" t="str">
-        <v>Ashoka Civil Works</v>
+        <v>Nova Instruments</v>
       </c>
       <c r="C36" t="str">
-        <v>S20/2025/021</v>
+        <v>S21/2025/021</v>
       </c>
       <c r="D36" t="str">
-        <v>24/11/2025</v>
+        <v>10/11/2025</v>
       </c>
       <c r="E36">
-        <v>143960</v>
+        <v>197060</v>
       </c>
       <c r="F36">
-        <v>122000</v>
+        <v>167000</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>30060</v>
       </c>
       <c r="H36">
-        <v>10980</v>
+        <v>0</v>
       </c>
       <c r="I36">
-        <v>10980</v>
+        <v>0</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -1907,7 +1907,7 @@
         <v>2025-12</v>
       </c>
       <c r="L36" t="str">
-        <v>13/12/2025</v>
+        <v>12/12/2025</v>
       </c>
       <c r="M36" t="str">
         <v>Yes</v>
@@ -1921,31 +1921,31 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>27AAFCA8801X1ZT</v>
+        <v>29AADCN3345Z1ZD</v>
       </c>
       <c r="B37" t="str">
-        <v>Ashoka Civil Works</v>
+        <v>Nova Instruments</v>
       </c>
       <c r="C37" t="str">
-        <v>S20/2025/022</v>
+        <v>S21/2025/022</v>
       </c>
       <c r="D37" t="str">
-        <v>16/11/2025</v>
+        <v>09/11/2025</v>
       </c>
       <c r="E37">
-        <v>149860</v>
+        <v>185260</v>
       </c>
       <c r="F37">
-        <v>127000</v>
+        <v>157000</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>28260</v>
       </c>
       <c r="H37">
-        <v>11430</v>
+        <v>0</v>
       </c>
       <c r="I37">
-        <v>11430</v>
+        <v>0</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -1954,7 +1954,7 @@
         <v>2025-12</v>
       </c>
       <c r="L37" t="str">
-        <v>09/12/2025</v>
+        <v>13/12/2025</v>
       </c>
       <c r="M37" t="str">
         <v>Yes</v>
@@ -1974,19 +1974,19 @@
         <v>Nova Instruments</v>
       </c>
       <c r="C38" t="str">
-        <v>S21/2025/021</v>
+        <v>S21/2025/023</v>
       </c>
       <c r="D38" t="str">
-        <v>26/11/2025</v>
+        <v>04/11/2025</v>
       </c>
       <c r="E38">
-        <v>191160</v>
+        <v>188800</v>
       </c>
       <c r="F38">
-        <v>162000</v>
+        <v>160000</v>
       </c>
       <c r="G38">
-        <v>29160</v>
+        <v>28800</v>
       </c>
       <c r="H38">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>2025-12</v>
       </c>
       <c r="L38" t="str">
-        <v>08/12/2025</v>
+        <v>14/12/2025</v>
       </c>
       <c r="M38" t="str">
         <v>Yes</v>
@@ -2015,31 +2015,31 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>29AADCN3345Z1ZD</v>
+        <v>27AAGFM1167A1ZO</v>
       </c>
       <c r="B39" t="str">
-        <v>Nova Instruments</v>
+        <v>Meridian Housekeeping</v>
       </c>
       <c r="C39" t="str">
-        <v>S21/2025/022</v>
+        <v>S22/2025/021</v>
       </c>
       <c r="D39" t="str">
         <v>05/11/2025</v>
       </c>
       <c r="E39">
-        <v>207680</v>
+        <v>220660</v>
       </c>
       <c r="F39">
-        <v>176000</v>
+        <v>187000</v>
       </c>
       <c r="G39">
-        <v>31680</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>16830</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>16830</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -2048,7 +2048,7 @@
         <v>2025-12</v>
       </c>
       <c r="L39" t="str">
-        <v>14/12/2025</v>
+        <v>15/12/2025</v>
       </c>
       <c r="M39" t="str">
         <v>Yes</v>
@@ -2062,25 +2062,25 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>29AADCN3345Z1ZD</v>
+        <v>24AAECC7789B1ZM</v>
       </c>
       <c r="B40" t="str">
-        <v>Nova Instruments</v>
+        <v>Coral Adhesives</v>
       </c>
       <c r="C40" t="str">
-        <v>S21/2025/023</v>
+        <v>S23/2025/021</v>
       </c>
       <c r="D40" t="str">
-        <v>25/11/2025</v>
+        <v>10/11/2025</v>
       </c>
       <c r="E40">
-        <v>208860</v>
+        <v>177000</v>
       </c>
       <c r="F40">
-        <v>177000</v>
+        <v>150000</v>
       </c>
       <c r="G40">
-        <v>31860</v>
+        <v>27000</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -2095,7 +2095,7 @@
         <v>2025-12</v>
       </c>
       <c r="L40" t="str">
-        <v>15/12/2025</v>
+        <v>09/12/2025</v>
       </c>
       <c r="M40" t="str">
         <v>Yes</v>
@@ -2109,31 +2109,31 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>27AAGFM1167A1ZO</v>
+        <v>09AAJFY5523C1Z3</v>
       </c>
       <c r="B41" t="str">
-        <v>Meridian Housekeeping</v>
+        <v>Yamuna Agro Products</v>
       </c>
       <c r="C41" t="str">
-        <v>S22/2025/021</v>
+        <v>S24/2025/021</v>
       </c>
       <c r="D41" t="str">
-        <v>02/11/2025</v>
+        <v>08/11/2025</v>
       </c>
       <c r="E41">
-        <v>202960</v>
+        <v>169920</v>
       </c>
       <c r="F41">
-        <v>172000</v>
+        <v>144000</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>25920</v>
       </c>
       <c r="H41">
-        <v>15480</v>
+        <v>0</v>
       </c>
       <c r="I41">
-        <v>15480</v>
+        <v>0</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -2142,7 +2142,7 @@
         <v>2025-12</v>
       </c>
       <c r="L41" t="str">
-        <v>12/12/2025</v>
+        <v>09/12/2025</v>
       </c>
       <c r="M41" t="str">
         <v>Yes</v>
@@ -2156,25 +2156,25 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>24AAECC7789B1ZM</v>
+        <v>09AAJFY5523C1Z3</v>
       </c>
       <c r="B42" t="str">
-        <v>Coral Adhesives</v>
+        <v>Yamuna Agro Products</v>
       </c>
       <c r="C42" t="str">
-        <v>S23/2025/021</v>
+        <v>S24/2025/022</v>
       </c>
       <c r="D42" t="str">
         <v>13/11/2025</v>
       </c>
       <c r="E42">
-        <v>202960</v>
+        <v>156940</v>
       </c>
       <c r="F42">
-        <v>172000</v>
+        <v>133000</v>
       </c>
       <c r="G42">
-        <v>30960</v>
+        <v>23940</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -2189,7 +2189,7 @@
         <v>2025-12</v>
       </c>
       <c r="L42" t="str">
-        <v>09/12/2025</v>
+        <v>12/12/2025</v>
       </c>
       <c r="M42" t="str">
         <v>Yes</v>
@@ -2209,10 +2209,10 @@
         <v>Yamuna Agro Products</v>
       </c>
       <c r="C43" t="str">
-        <v>S24/2025/021</v>
+        <v>S24/2025/023</v>
       </c>
       <c r="D43" t="str">
-        <v>25/11/2025</v>
+        <v>24/11/2025</v>
       </c>
       <c r="E43">
         <v>167560</v>
@@ -2236,7 +2236,7 @@
         <v>2025-12</v>
       </c>
       <c r="L43" t="str">
-        <v>15/12/2025</v>
+        <v>11/12/2025</v>
       </c>
       <c r="M43" t="str">
         <v>Yes</v>
@@ -2250,31 +2250,31 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>09AAJFY5523C1Z3</v>
+        <v>27AABCZ9934D1Z1</v>
       </c>
       <c r="B44" t="str">
-        <v>Yamuna Agro Products</v>
+        <v>Zenith Tooling</v>
       </c>
       <c r="C44" t="str">
-        <v>S24/2025/022</v>
+        <v>S25/2025/021</v>
       </c>
       <c r="D44" t="str">
-        <v>25/11/2025</v>
+        <v>02/11/2025</v>
       </c>
       <c r="E44">
-        <v>143960</v>
+        <v>50740</v>
       </c>
       <c r="F44">
-        <v>122000</v>
+        <v>43000</v>
       </c>
       <c r="G44">
-        <v>21960</v>
+        <v>0</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>3870</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>3870</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>2025-12</v>
       </c>
       <c r="L44" t="str">
-        <v>13/12/2025</v>
+        <v>16/12/2025</v>
       </c>
       <c r="M44" t="str">
         <v>Yes</v>
@@ -2292,106 +2292,12 @@
         <v/>
       </c>
       <c r="O44" t="str">
-        <v>N</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v>09AAJFY5523C1Z3</v>
-      </c>
-      <c r="B45" t="str">
-        <v>Yamuna Agro Products</v>
-      </c>
-      <c r="C45" t="str">
-        <v>S24/2025/023</v>
-      </c>
-      <c r="D45" t="str">
-        <v>13/11/2025</v>
-      </c>
-      <c r="E45">
-        <v>159300</v>
-      </c>
-      <c r="F45">
-        <v>135000</v>
-      </c>
-      <c r="G45">
-        <v>24300</v>
-      </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
-      <c r="I45">
-        <v>0</v>
-      </c>
-      <c r="J45">
-        <v>0</v>
-      </c>
-      <c r="K45" t="str">
-        <v>2025-12</v>
-      </c>
-      <c r="L45" t="str">
-        <v>15/12/2025</v>
-      </c>
-      <c r="M45" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="N45" t="str">
-        <v/>
-      </c>
-      <c r="O45" t="str">
-        <v>N</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v>27AABCZ9934D1Z1</v>
-      </c>
-      <c r="B46" t="str">
-        <v>Zenith Tooling</v>
-      </c>
-      <c r="C46" t="str">
-        <v>S25/2025/021</v>
-      </c>
-      <c r="D46" t="str">
-        <v>09/11/2025</v>
-      </c>
-      <c r="E46">
-        <v>35400</v>
-      </c>
-      <c r="F46">
-        <v>30000</v>
-      </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-      <c r="H46">
-        <v>2700</v>
-      </c>
-      <c r="I46">
-        <v>2700</v>
-      </c>
-      <c r="J46">
-        <v>0</v>
-      </c>
-      <c r="K46" t="str">
-        <v>2025-12</v>
-      </c>
-      <c r="L46" t="str">
-        <v>11/12/2025</v>
-      </c>
-      <c r="M46" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="N46" t="str">
-        <v/>
-      </c>
-      <c r="O46" t="str">
         <v>N</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O46"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O44"/>
   </ignoredErrors>
 </worksheet>
 </file>
